--- a/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="281">
   <si>
     <r>
       <rPr>
@@ -33,6 +33,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">꽃 타령</t>
     </r>
@@ -64,6 +65,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">파일</t>
     </r>
@@ -83,6 +85,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">민요</t>
     </r>
@@ -100,6 +103,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">꽃 타령 </t>
     </r>
@@ -117,6 +121,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">자진모리</t>
     </r>
@@ -149,6 +154,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">박자 </t>
     </r>
@@ -168,6 +174,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">행수</t>
     </r>
@@ -187,6 +194,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간</t>
     </r>
@@ -207,6 +215,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">비고</t>
     </r>
@@ -226,6 +235,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">노란 칸</t>
     </r>
@@ -250,6 +260,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">팔레트 외 글자</t>
     </r>
@@ -269,6 +280,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">주황 칸</t>
     </r>
@@ -301,6 +313,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">비고 </t>
     </r>
@@ -326,6 +339,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">민요채보</t>
     </r>
@@ -343,6 +357,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">꽃 타령</t>
     </r>
@@ -362,6 +377,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">인쇄 </t>
     </r>
@@ -379,6 +395,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간 양식</t>
     </r>
@@ -396,6 +413,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄번호 </t>
     </r>
@@ -413,6 +431,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간 </t>
     </r>
@@ -430,6 +449,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">굵은 선 </t>
     </r>
@@ -447,6 +467,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">칸마다 → </t>
     </r>
@@ -464,6 +485,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">내용은 오른쪽 </t>
     </r>
@@ -481,6 +503,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄부터 왼쪽 </t>
     </r>
@@ -498,6 +521,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄까지</t>
     </r>
@@ -515,6 +539,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄은 비어 보조표시만 있어 범위에서 제외</t>
     </r>
@@ -532,6 +557,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사함</t>
     </r>
@@ -549,6 +575,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">꽃 사시오</t>
     </r>
@@ -566,6 +593,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">후렴이 </t>
     </r>
@@ -583,6 +611,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄</t>
     </r>
@@ -600,6 +629,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄에서 반복됨</t>
     </r>
@@ -617,6 +647,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵</t>
     </r>
@@ -634,6 +665,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">청</t>
     </r>
@@ -651,6 +683,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">亻</t>
     </r>
@@ -668,6 +701,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">배</t>
     </r>
@@ -685,6 +719,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">중성 변 구별이 흐린 칸은 비고에 표기</t>
     </r>
@@ -702,6 +737,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">손채보 </t>
     </r>
@@ -719,6 +755,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">장</t>
     </r>
@@ -736,6 +773,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">재판독</t>
     </r>
@@ -761,6 +799,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">원본처럼 오른쪽이 </t>
     </r>
@@ -778,6 +817,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄</t>
     </r>
@@ -795,6 +835,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">악보 시트도 같은 배치</t>
     </r>
@@ -812,6 +853,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
     </r>
@@ -829,6 +871,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">빈 행 </t>
     </r>
@@ -846,6 +889,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개</t>
     </r>
@@ -863,6 +907,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
     </r>
@@ -880,6 +925,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
     </r>
@@ -897,6 +943,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">율명</t>
     </r>
@@ -914,6 +961,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">가사</t>
     </r>
@@ -931,6 +979,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
     </r>
@@ -948,6 +997,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간</t>
     </r>
@@ -965,6 +1015,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">박자는 </t>
     </r>
@@ -982,6 +1033,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
     </r>
@@ -999,6 +1051,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">율명 글자는 가사의 두 배</t>
     </r>
@@ -1016,6 +1069,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">인쇄는 </t>
     </r>
@@ -1033,6 +1087,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">세로</t>
     </r>
@@ -1050,6 +1105,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">원본 한 페이지 </t>
     </r>
@@ -1067,6 +1123,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">종이 한 장</t>
     </r>
@@ -1084,6 +1141,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간 번호 열</t>
     </r>
@@ -1101,6 +1159,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
     </r>
@@ -1118,6 +1177,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">번째 행이 정간 </t>
     </r>
@@ -1135,6 +1195,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
     </r>
@@ -1152,6 +1213,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">제목 병합도 풀지 말 것</t>
     </r>
@@ -1169,6 +1231,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">한 장이 </t>
     </r>
@@ -1186,6 +1249,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄을 넘으면 </t>
     </r>
@@ -1203,6 +1267,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">줄씩 다음 페이지</t>
     </r>
@@ -1216,6 +1281,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간 안에서 위→아래 순서</t>
     </r>
@@ -1233,6 +1299,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
     </r>
@@ -1250,6 +1317,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">앱과 같음</t>
     </r>
@@ -1272,6 +1340,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">– 연음 </t>
     </r>
@@ -1289,6 +1358,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">쉼 </t>
     </r>
@@ -1306,6 +1376,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">점 </t>
     </r>
@@ -1323,6 +1394,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">동그라미 </t>
     </r>
@@ -1340,6 +1412,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">두 점 </t>
     </r>
@@ -1357,6 +1430,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간 경계 표시 </t>
     </r>
@@ -1374,6 +1448,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">／ 사선 </t>
     </r>
@@ -1391,6 +1466,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">／ 는 화면 표시 전용</t>
     </r>
@@ -1419,6 +1495,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">율명</t>
     </r>
@@ -1436,6 +1513,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">기호표에 없는 글자 </t>
     </r>
@@ -1453,6 +1531,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">포함</t>
     </r>
@@ -1470,6 +1549,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">반드시 수정</t>
     </r>
@@ -1483,6 +1563,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">악보 시트를 고쳐 </t>
     </r>
@@ -1500,6 +1581,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">로 저장한 뒤 </t>
     </r>
@@ -1517,6 +1599,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">작업</t>
     </r>
@@ -1534,6 +1617,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">실행 → </t>
     </r>
@@ -1551,6 +1635,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">반영</t>
     </r>
@@ -1568,6 +1653,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정보</t>
     </r>
@@ -1585,6 +1671,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
     </r>
@@ -1608,6 +1695,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">율명</t>
     </r>
@@ -1627,6 +1715,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">판독</t>
     </r>
@@ -1648,6 +1737,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">율명</t>
     </r>
@@ -1667,6 +1757,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">앱</t>
     </r>
@@ -1696,6 +1787,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1713,6 +1805,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1746,6 +1839,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">湳</t>
     </r>
@@ -1763,6 +1857,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1778,6 +1873,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">湳</t>
     </r>
@@ -1795,6 +1891,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵南</t>
     </r>
@@ -1812,6 +1909,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">추정</t>
     </r>
@@ -1822,6 +1920,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1839,6 +1938,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1856,6 +1956,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1874,6 +1975,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潕</t>
     </r>
@@ -1891,6 +1993,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -1909,6 +2012,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潕</t>
     </r>
@@ -1926,6 +2030,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵無</t>
     </r>
@@ -1943,6 +2048,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">추정</t>
     </r>
@@ -1956,6 +2062,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -1973,6 +2080,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -2003,6 +2111,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㑖</t>
     </r>
@@ -2020,6 +2129,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㑖</t>
     </r>
@@ -2044,6 +2154,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">亻仲 </t>
     </r>
@@ -2061,6 +2172,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개 추정</t>
     </r>
@@ -2071,6 +2183,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2088,6 +2201,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2121,6 +2235,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -2138,6 +2253,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2155,6 +2271,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2172,6 +2289,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2189,6 +2307,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2204,6 +2323,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -2221,6 +2341,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2238,6 +2359,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -2256,6 +2378,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2273,6 +2396,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2299,6 +2423,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -2316,6 +2441,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2340,6 +2466,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2360,6 +2487,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2376,6 +2504,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2393,6 +2522,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2411,6 +2541,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2428,6 +2559,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2445,6 +2577,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -2462,6 +2595,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2480,6 +2614,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -2497,6 +2632,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵太</t>
     </r>
@@ -2519,6 +2655,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2536,6 +2673,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2566,6 +2704,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2583,6 +2722,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2601,6 +2741,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -2618,6 +2759,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2648,6 +2790,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2665,6 +2808,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -2682,6 +2826,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2699,6 +2844,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -2716,6 +2862,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2733,6 +2880,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -2759,6 +2907,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2776,6 +2925,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -2793,6 +2943,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -2820,6 +2971,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2846,6 +2998,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2863,6 +3016,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2880,6 +3034,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -2901,6 +3056,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -2918,6 +3074,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2935,6 +3092,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -2953,6 +3111,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵黃</t>
     </r>
@@ -2970,6 +3129,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -2987,6 +3147,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵黃</t>
     </r>
@@ -2997,6 +3158,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -3014,6 +3176,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3031,6 +3194,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3055,6 +3219,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">동그라미 </t>
     </r>
@@ -3072,6 +3237,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개</t>
     </r>
@@ -3082,6 +3248,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3099,6 +3266,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -3132,6 +3300,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3155,6 +3324,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -3172,6 +3342,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -3192,6 +3363,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -3209,6 +3381,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3233,6 +3406,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3250,6 +3424,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3267,6 +3442,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -3284,6 +3460,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">둘째 흐림</t>
     </r>
@@ -3294,6 +3471,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3311,6 +3489,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3326,6 +3505,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3343,6 +3523,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -3360,6 +3541,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵黃</t>
     </r>
@@ -3377,6 +3559,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵仲</t>
     </r>
@@ -3396,6 +3579,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3416,6 +3600,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3426,6 +3611,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">潢</t>
     </r>
@@ -3443,6 +3629,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -3460,6 +3647,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵黃</t>
     </r>
@@ -3477,6 +3665,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵太</t>
     </r>
@@ -3487,6 +3676,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">太</t>
     </r>
@@ -3504,6 +3694,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -3521,6 +3712,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -3538,6 +3730,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -3555,6 +3748,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">氵太 </t>
     </r>
@@ -3572,6 +3766,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개</t>
     </r>
@@ -3585,6 +3780,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">汰</t>
     </r>
@@ -3602,6 +3798,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">南</t>
     </r>
@@ -3634,6 +3831,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -3651,6 +3849,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -3675,6 +3874,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3692,6 +3892,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3716,6 +3917,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">無</t>
     </r>
@@ -3733,6 +3935,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">姑</t>
     </r>
@@ -3750,6 +3953,7 @@
         <sz val="11"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">仲</t>
     </r>
@@ -3808,6 +4012,7 @@
         <sz val="24"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞
 㳞</t>
@@ -3843,6 +4048,7 @@
         <sz val="24"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞</t>
     </r>
@@ -3854,7 +4060,8 @@
   </si>
   <si>
     <t xml:space="preserve">南
-– 南</t>
+– 
+南</t>
   </si>
   <si>
     <t xml:space="preserve">웃
@@ -3866,6 +4073,36 @@
 로</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">湳
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㳞
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">–</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">파
 란</t>
   </si>
@@ -4018,6 +4255,7 @@
         <sz val="24"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㴌</t>
     </r>
@@ -4044,6 +4282,7 @@
         <sz val="24"/>
         <rFont val="나눔고딕"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">㳞
 㴌</t>
@@ -4142,11 +4381,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4168,6 +4408,7 @@
       <sz val="11"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -4187,22 +4428,30 @@
       <sz val="24"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="24"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="나눔고딕"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4324,7 +4573,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4603,13 +4852,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="85.27"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4617,7 +4866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -4625,19 +4874,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -4645,7 +4894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -4653,7 +4902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -4661,7 +4910,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -4669,7 +4918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -4677,7 +4926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
@@ -4685,7 +4934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -4694,7 +4943,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -4702,7 +4951,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
@@ -4717,7 +4966,7 @@
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="52" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
@@ -4725,7 +4974,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
@@ -4733,7 +4982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -4741,7 +4990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
@@ -4749,7 +4998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>33</v>
       </c>
@@ -4757,7 +5006,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
@@ -4794,7 +5043,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -4829,7 +5078,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
@@ -4860,7 +5109,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>1</v>
       </c>
@@ -4891,7 +5140,7 @@
       <c r="J3" s="6"/>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="n">
         <v>1</v>
       </c>
@@ -4922,7 +5171,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -4953,7 +5202,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
         <v>1</v>
       </c>
@@ -4982,7 +5231,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>1</v>
       </c>
@@ -5011,7 +5260,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
         <v>1</v>
       </c>
@@ -5040,7 +5289,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>1</v>
       </c>
@@ -5069,7 +5318,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
@@ -5102,7 +5351,7 @@
       </c>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>1</v>
       </c>
@@ -5133,7 +5382,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
         <v>1</v>
       </c>
@@ -5166,7 +5415,7 @@
       </c>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>1</v>
       </c>
@@ -5197,7 +5446,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
         <v>1</v>
       </c>
@@ -5230,7 +5479,7 @@
       </c>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>1</v>
       </c>
@@ -5263,7 +5512,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
         <v>1</v>
       </c>
@@ -5294,7 +5543,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>1</v>
       </c>
@@ -5325,7 +5574,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
         <v>1</v>
       </c>
@@ -5358,7 +5607,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>1</v>
       </c>
@@ -5389,7 +5638,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
         <v>1</v>
       </c>
@@ -5420,7 +5669,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>1</v>
       </c>
@@ -5451,7 +5700,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
         <v>1</v>
       </c>
@@ -5482,7 +5731,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>1</v>
       </c>
@@ -5513,7 +5762,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
         <v>1</v>
       </c>
@@ -5540,7 +5789,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>1</v>
       </c>
@@ -5569,7 +5818,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
         <v>1</v>
       </c>
@@ -5600,7 +5849,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="24.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>1</v>
       </c>
@@ -5633,7 +5882,7 @@
       </c>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
         <v>1</v>
       </c>
@@ -5664,7 +5913,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>1</v>
       </c>
@@ -5695,7 +5944,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
         <v>1</v>
       </c>
@@ -5728,7 +5977,7 @@
       </c>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="24.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>1</v>
       </c>
@@ -5759,7 +6008,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
         <v>1</v>
       </c>
@@ -5790,7 +6039,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>1</v>
       </c>
@@ -5823,7 +6072,7 @@
       </c>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
         <v>1</v>
       </c>
@@ -5854,7 +6103,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="24.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>1</v>
       </c>
@@ -5887,7 +6136,7 @@
       </c>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
         <v>1</v>
       </c>
@@ -5920,7 +6169,7 @@
       </c>
       <c r="K36" s="8"/>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
         <v>1</v>
       </c>
@@ -5953,7 +6202,7 @@
       </c>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
         <v>1</v>
       </c>
@@ -5984,7 +6233,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
         <v>1</v>
       </c>
@@ -6015,7 +6264,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
         <v>1</v>
       </c>
@@ -6046,7 +6295,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="8"/>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
         <v>1</v>
       </c>
@@ -6077,7 +6326,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
         <v>1</v>
       </c>
@@ -6108,7 +6357,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
         <v>1</v>
       </c>
@@ -6139,7 +6388,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
         <v>1</v>
       </c>
@@ -6170,7 +6419,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="8"/>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
         <v>1</v>
       </c>
@@ -6203,7 +6452,7 @@
       </c>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
         <v>1</v>
       </c>
@@ -6234,7 +6483,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
         <v>1</v>
       </c>
@@ -6265,7 +6514,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
         <v>1</v>
       </c>
@@ -6296,7 +6545,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
         <v>1</v>
       </c>
@@ -6327,7 +6576,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
         <v>1</v>
       </c>
@@ -6360,7 +6609,7 @@
       </c>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
         <v>1</v>
       </c>
@@ -6391,7 +6640,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
         <v>1</v>
       </c>
@@ -6422,7 +6671,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
         <v>1</v>
       </c>
@@ -6453,7 +6702,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
         <v>1</v>
       </c>
@@ -6484,7 +6733,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>1</v>
       </c>
@@ -6515,7 +6764,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
         <v>1</v>
       </c>
@@ -6542,7 +6791,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>1</v>
       </c>
@@ -6571,7 +6820,7 @@
       </c>
       <c r="K57" s="8"/>
     </row>
-    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
         <v>1</v>
       </c>
@@ -6602,7 +6851,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>1</v>
       </c>
@@ -6633,7 +6882,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="8"/>
     </row>
-    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
         <v>1</v>
       </c>
@@ -6664,7 +6913,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>1</v>
       </c>
@@ -6697,7 +6946,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
         <v>1</v>
       </c>
@@ -6730,7 +6979,7 @@
       </c>
       <c r="K62" s="8"/>
     </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>1</v>
       </c>
@@ -6763,7 +7012,7 @@
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
         <v>1</v>
       </c>
@@ -6794,7 +7043,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>1</v>
       </c>
@@ -6825,7 +7074,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="8"/>
     </row>
-    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
         <v>1</v>
       </c>
@@ -6858,7 +7107,7 @@
       </c>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>1</v>
       </c>
@@ -6889,7 +7138,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="8"/>
     </row>
-    <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>1</v>
       </c>
@@ -6922,7 +7171,7 @@
       </c>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>1</v>
       </c>
@@ -6953,7 +7202,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="8"/>
     </row>
-    <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
         <v>1</v>
       </c>
@@ -6986,7 +7235,7 @@
       </c>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>1</v>
       </c>
@@ -7017,7 +7266,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>1</v>
       </c>
@@ -7050,7 +7299,7 @@
       </c>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="24.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>1</v>
       </c>
@@ -7081,7 +7330,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>1</v>
       </c>
@@ -7114,7 +7363,7 @@
       </c>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>1</v>
       </c>
@@ -7145,7 +7394,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
         <v>1</v>
       </c>
@@ -7178,7 +7427,7 @@
       </c>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>1</v>
       </c>
@@ -7211,7 +7460,7 @@
       </c>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
         <v>1</v>
       </c>
@@ -7244,7 +7493,7 @@
       </c>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>1</v>
       </c>
@@ -7275,7 +7524,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="8"/>
     </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
         <v>1</v>
       </c>
@@ -7308,7 +7557,7 @@
       </c>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>1</v>
       </c>
@@ -7339,7 +7588,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
         <v>1</v>
       </c>
@@ -7370,7 +7619,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>1</v>
       </c>
@@ -7401,7 +7650,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="8"/>
     </row>
-    <row r="84" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>1</v>
       </c>
@@ -7432,7 +7681,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>1</v>
       </c>
@@ -7463,7 +7712,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
         <v>1</v>
       </c>
@@ -7496,7 +7745,7 @@
       </c>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>1</v>
       </c>
@@ -7527,7 +7776,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="8"/>
     </row>
-    <row r="88" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
         <v>1</v>
       </c>
@@ -7560,7 +7809,7 @@
       </c>
       <c r="K88" s="8"/>
     </row>
-    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
         <v>1</v>
       </c>
@@ -7593,7 +7842,7 @@
       </c>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
         <v>1</v>
       </c>
@@ -7626,7 +7875,7 @@
       </c>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>1</v>
       </c>
@@ -7657,7 +7906,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
         <v>1</v>
       </c>
@@ -7688,7 +7937,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="8"/>
     </row>
-    <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="26.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>1</v>
       </c>
@@ -7719,7 +7968,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
         <v>1</v>
       </c>
@@ -7752,7 +8001,7 @@
       </c>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>1</v>
       </c>
@@ -7783,7 +8032,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="8"/>
     </row>
-    <row r="96" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="39.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
         <v>1</v>
       </c>
@@ -7814,7 +8063,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="8"/>
     </row>
-    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>1</v>
       </c>
@@ -7867,22 +8116,22 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
         <v>208</v>
       </c>
@@ -7898,7 +8147,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="s">
         <v>209</v>
       </c>
@@ -7936,7 +8185,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="16" t="s">
         <v>216</v>
       </c>
@@ -7974,7 +8223,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
         <v>47</v>
       </c>
@@ -7994,10 +8243,10 @@
         <v>224</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>83</v>
@@ -8010,13 +8259,11 @@
       </c>
       <c r="M5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>210</v>
-      </c>
+      <c r="C6" s="20"/>
       <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
@@ -8027,7 +8274,7 @@
         <v>86</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>118</v>
@@ -8039,25 +8286,25 @@
         <v>86</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L6" s="12" t="s">
         <v>152</v>
       </c>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>209</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>152</v>
@@ -8067,7 +8314,7 @@
         <v>166</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>152</v>
@@ -8078,28 +8325,28 @@
       </c>
       <c r="M7" s="13"/>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>152</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>152</v>
@@ -8110,26 +8357,26 @@
       </c>
       <c r="M8" s="17"/>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="14" t="s">
         <v>209</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>177</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="17"/>
       <c r="H9" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="17"/>
@@ -8138,7 +8385,7 @@
       </c>
       <c r="M9" s="17"/>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="14" t="s">
         <v>64</v>
       </c>
@@ -8170,7 +8417,7 @@
       </c>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="14" t="s">
         <v>203</v>
       </c>
@@ -8178,37 +8425,37 @@
         <v>215</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>209</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L11" s="14" t="s">
         <v>55</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
         <v>205</v>
       </c>
@@ -8216,37 +8463,37 @@
         <v>215</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>58</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>216</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L12" s="12" t="s">
         <v>58</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
         <v>73</v>
       </c>
@@ -8254,66 +8501,66 @@
         <v>215</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>47</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>47</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L13" s="14" t="s">
         <v>209</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>215</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>48</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>48</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L14" s="12" t="s">
         <v>64</v>
@@ -8322,7 +8569,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
         <v>145</v>
       </c>
@@ -8330,28 +8577,28 @@
         <v>215</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L15" s="14" t="s">
         <v>203</v>
@@ -8360,7 +8607,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
         <v>81</v>
       </c>
@@ -8368,28 +8615,28 @@
         <v>221</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>220</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L16" s="14" t="s">
         <v>205</v>
@@ -8398,7 +8645,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
         <v>83</v>
       </c>
@@ -8406,28 +8653,28 @@
         <v>224</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>166</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L17" s="12" t="s">
         <v>73</v>
@@ -8436,12 +8683,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>168</v>
@@ -8465,10 +8712,10 @@
         <v>64</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M18" s="20" t="s">
         <v>215</v>

--- a/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
@@ -31,7 +31,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -63,7 +63,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -83,7 +83,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -101,7 +101,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -119,7 +119,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -152,7 +152,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -172,7 +172,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -192,7 +192,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -213,7 +213,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -233,7 +233,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -258,7 +258,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -278,7 +278,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -311,7 +311,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -337,7 +337,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -355,7 +355,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -375,7 +375,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -393,7 +393,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -411,7 +411,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -429,7 +429,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -447,7 +447,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -465,7 +465,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -483,7 +483,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -501,7 +501,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -519,7 +519,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -537,7 +537,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -555,7 +555,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -573,7 +573,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -591,7 +591,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -609,7 +609,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -627,7 +627,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -645,7 +645,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -663,7 +663,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -681,7 +681,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -699,7 +699,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -717,7 +717,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -735,7 +735,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -753,7 +753,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -771,7 +771,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -797,7 +797,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -815,7 +815,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -833,7 +833,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -851,7 +851,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -869,7 +869,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -887,7 +887,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -905,7 +905,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -923,7 +923,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -941,7 +941,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -959,7 +959,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -977,7 +977,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -995,7 +995,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1013,7 +1013,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1031,7 +1031,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1049,7 +1049,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1067,7 +1067,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1085,7 +1085,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1103,7 +1103,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1121,7 +1121,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1139,7 +1139,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1157,7 +1157,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1175,7 +1175,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1193,7 +1193,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1211,7 +1211,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1229,7 +1229,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1247,7 +1247,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1265,7 +1265,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1279,7 +1279,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1297,7 +1297,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1315,7 +1315,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1338,7 +1338,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1356,7 +1356,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1374,7 +1374,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1392,7 +1392,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1410,7 +1410,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1428,7 +1428,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1446,7 +1446,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1464,7 +1464,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1493,7 +1493,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1511,7 +1511,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1529,7 +1529,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1547,7 +1547,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1561,7 +1561,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1579,7 +1579,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1597,7 +1597,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1615,7 +1615,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1633,7 +1633,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1651,7 +1651,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1669,7 +1669,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1693,7 +1693,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1713,7 +1713,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1735,7 +1735,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1755,7 +1755,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1785,7 +1785,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1803,7 +1803,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1837,7 +1837,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1855,7 +1855,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1871,7 +1871,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1889,7 +1889,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1907,7 +1907,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1918,7 +1918,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1936,7 +1936,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1954,7 +1954,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1973,7 +1973,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -1991,7 +1991,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2010,7 +2010,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2028,7 +2028,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2046,7 +2046,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2060,7 +2060,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2078,7 +2078,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2109,7 +2109,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2127,7 +2127,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2152,7 +2152,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2170,7 +2170,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2181,7 +2181,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2199,7 +2199,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2233,7 +2233,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2251,7 +2251,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2269,7 +2269,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2287,7 +2287,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2305,7 +2305,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2321,7 +2321,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2339,7 +2339,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2357,7 +2357,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2376,7 +2376,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2394,7 +2394,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2421,7 +2421,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2439,7 +2439,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2464,7 +2464,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2485,7 +2485,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2502,7 +2502,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2520,7 +2520,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2539,7 +2539,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2557,7 +2557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2575,7 +2575,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2593,7 +2593,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2612,7 +2612,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2630,7 +2630,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2653,7 +2653,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2671,7 +2671,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2702,7 +2702,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2720,7 +2720,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2739,7 +2739,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2757,7 +2757,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2788,7 +2788,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2806,7 +2806,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2824,7 +2824,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2842,7 +2842,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2860,7 +2860,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2878,7 +2878,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2905,7 +2905,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2923,7 +2923,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2941,7 +2941,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2969,7 +2969,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -2996,7 +2996,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3014,7 +3014,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3032,7 +3032,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3054,7 +3054,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3072,7 +3072,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3090,7 +3090,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3109,7 +3109,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3127,7 +3127,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3145,7 +3145,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3156,7 +3156,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3174,7 +3174,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3192,7 +3192,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3217,7 +3217,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3235,7 +3235,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3246,7 +3246,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3264,7 +3264,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3298,7 +3298,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3322,7 +3322,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3340,7 +3340,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3361,7 +3361,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3379,7 +3379,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3404,7 +3404,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3422,7 +3422,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3440,7 +3440,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3458,7 +3458,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3469,7 +3469,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3487,7 +3487,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3503,7 +3503,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3521,7 +3521,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3539,7 +3539,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3557,7 +3557,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3577,7 +3577,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3598,7 +3598,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3609,7 +3609,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3627,7 +3627,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3645,7 +3645,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3663,7 +3663,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3674,7 +3674,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3692,7 +3692,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3710,7 +3710,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3728,7 +3728,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3746,7 +3746,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3764,7 +3764,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3778,7 +3778,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3796,7 +3796,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3829,7 +3829,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3847,7 +3847,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3872,7 +3872,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3890,7 +3890,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3915,7 +3915,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3933,7 +3933,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3951,7 +3951,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -3999,7 +3999,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -4009,8 +4008,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4035,7 +4033,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -4045,8 +4042,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4075,8 +4071,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4085,8 +4080,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">㳞
@@ -4094,8 +4088,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4242,7 +4235,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -4252,8 +4244,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4269,7 +4260,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -4279,8 +4269,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
-        <rFont val="나눔고딕"/>
+        <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
@@ -4381,32 +4370,32 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -4426,19 +4415,19 @@
     <font>
       <b val="true"/>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -4450,8 +4439,14 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="나눔고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4544,7 +4539,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4630,6 +4625,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8116,608 +8155,608 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="23" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="23" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="23" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="23" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="23" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="23" width="5.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="26" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="29" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="M6" s="20"/>
+      <c r="M6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="12" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="12" t="s">
+      <c r="G8" s="29"/>
+      <c r="H8" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="12" t="s">
+      <c r="K8" s="29"/>
+      <c r="L8" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="M8" s="17"/>
+      <c r="M8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="12" t="s">
+      <c r="F9" s="25"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="12" t="s">
+      <c r="J9" s="25"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="M9" s="17"/>
+      <c r="M9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="12" t="s">
+      <c r="G10" s="32"/>
+      <c r="H10" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="12" t="s">
+      <c r="K10" s="31"/>
+      <c r="L10" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="20"/>
+      <c r="M10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="28" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="29" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="30" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="M14" s="20" t="s">
+      <c r="M14" s="31" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="M15" s="17" t="s">
+      <c r="M15" s="29" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="M16" s="17" t="s">
+      <c r="M16" s="29" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="29" t="s">
         <v>275</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="L17" s="12" t="s">
+      <c r="L17" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="M17" s="17" t="s">
+      <c r="M17" s="29" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="L18" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="31" t="s">
         <v>215</v>
       </c>
     </row>

--- a/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
@@ -4463,10 +4463,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
@@ -27,113 +27,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="281">
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 타령</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CSV </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">파일</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sheets/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">민요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/csv/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 타령 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">자진모리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)-2.csv</t>
-    </r>
+    <t xml:space="preserve">꽃 타령-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSV 파일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sheets/민요/csv/꽃 타령 (자진모리)-2.csv</t>
   </si>
   <si>
     <t xml:space="preserve">부제</t>
@@ -148,56 +48,10 @@
     <t xml:space="preserve">쪽</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">박자 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">행수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/4 / 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
+    <t xml:space="preserve">박자 / 행수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/4 / 16정간</t>
   </si>
   <si>
     <t xml:space="preserve">페이지</t>
@@ -209,91 +63,13 @@
     <t xml:space="preserve">정간 수</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">비고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">노란 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">비고(노란 칸)</t>
   </si>
   <si>
     <t xml:space="preserve">31</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">팔레트 외 글자</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">주황 칸</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">팔레트 외 글자(주황 칸)</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -308,24 +84,7 @@
     <t xml:space="preserve">확인 필요</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">비고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32%</t>
-    </r>
+    <t xml:space="preserve">비고 32%</t>
   </si>
   <si>
     <t xml:space="preserve">원본 이미지</t>
@@ -334,458 +93,10 @@
     <t xml:space="preserve">판독 메모</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">민요채보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 타령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">인쇄 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간 양식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄번호 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8~1, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1~16, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">굵은 선 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">칸마다 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4/4·16). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">내용은 오른쪽 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄부터 왼쪽 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄까지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 7·8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄은 비어 보조표시만 있어 범위에서 제외</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 사시오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">후렴이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄에서 반복됨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">亻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">배</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">중성 변 구별이 흐린 칸은 비고에 표기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">손채보 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A4 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">재판독</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
+    <t xml:space="preserve">민요채보-2/꽃 타령.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인쇄 16정간 양식(줄번호 8~1, 정간 1~16, 굵은 선 4칸마다 → 4/4·16). 내용은 오른쪽 1줄부터 왼쪽 6줄까지, 7·8줄은 비어 보조표시만 있어 범위에서 제외. 각 율명 줄 바로 오른쪽 좁은 칸의 가사를 전사함. "꽃 사시오" 후렴이 1줄·6줄에서 반복됨. 氵(청)·亻(배)·중성 변 구별이 흐린 칸은 비고에 표기. 손채보 A4 1장. AI 재판독.</t>
   </si>
   <si>
     <t xml:space="preserve">범례</t>
@@ -794,691 +105,19 @@
     <t xml:space="preserve">줄 순서</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">원본처럼 오른쪽이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">악보 시트도 같은 배치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">여러 페이지는 악보 시트 아래쪽으로 이어짐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">빈 행 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">인쇄 시 페이지마다 새 종이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄은 항상 맨 오른쪽 두 열</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">가사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">). 3/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">박자는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, 4/4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">박자는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간마다 가사 칸 가로선을 묶음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">율명 글자는 가사의 두 배</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">인쇄는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">세로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">원본 한 페이지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">종이 한 장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간 번호 열</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">머리 행 없음 — 제목 행 아래 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">번째 행이 정간 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">이므로 행을 지우거나 끼워 넣지 말고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">제목 병합도 풀지 말 것</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">한 장이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄을 넘으면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">줄씩 다음 페이지</t>
-    </r>
+    <t xml:space="preserve">원본처럼 오른쪽이 1줄. 악보 시트도 같은 배치. 여러 페이지는 악보 시트 아래쪽으로 이어짐(빈 행 1개, 인쇄 시 페이지마다 새 종이). 1줄은 항상 맨 오른쪽 두 열(율명, 가사). 3/4 박자는 3정간, 4/4 박자는 4정간마다 가사 칸 가로선을 묶음. 율명 글자는 가사의 두 배. 인쇄는 A4 세로, 원본 한 페이지 = 종이 한 장. 정간 번호 열·머리 행 없음 — 제목 행 아래 n번째 행이 정간 n이므로 행을 지우거나 끼워 넣지 말고, 제목 병합도 풀지 말 것. 한 장이 10줄을 넘으면 10줄씩 다음 페이지</t>
   </si>
   <si>
     <t xml:space="preserve">율명 칸</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간 안에서 위→아래 순서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">칸 안 줄바꿈으로 구분 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">앱과 같음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">정간 안에서 위→아래 순서, 칸 안 줄바꿈으로 구분 (앱과 같음)</t>
   </si>
   <si>
     <t xml:space="preserve">기호</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">– 연음 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· △ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">쉼 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ○ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">동그라미 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ⁚ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">두 점 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· ‹ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간 경계 표시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">／ 사선 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(· ○ ⁚ ‹ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">／ 는 화면 표시 전용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
   </si>
   <si>
     <t xml:space="preserve">노란 칸</t>
@@ -1490,191 +129,13 @@
     <t xml:space="preserve">주황 칸</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">기호표에 없는 글자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">포함</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">반드시 수정</t>
-    </r>
+    <t xml:space="preserve">율명·기호표에 없는 글자 (? 포함) — 반드시 수정</t>
   </si>
   <si>
     <t xml:space="preserve">수정 방법</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">악보 시트를 고쳐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.xlsx </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">로 저장한 뒤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">작업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/xlsx_to_csv.py </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">실행 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">csv </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">반영</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">정간목록 시트는 반영 안 됨</t>
-    </r>
+    <t xml:space="preserve">악보 시트를 고쳐 .xlsx 로 저장한 뒤 _작업/xlsx_to_csv.py 실행 → csv 반영. 정보·정간목록 시트는 반영 안 됨</t>
   </si>
   <si>
     <t xml:space="preserve">줄</t>
@@ -1689,88 +150,10 @@
     <t xml:space="preserve">박</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">판독</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">율명</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">앱</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">율명(판독)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">율명(앱)</t>
   </si>
   <si>
     <t xml:space="preserve">가사</t>
@@ -1782,33 +165,7 @@
     <t xml:space="preserve">확인 필요 글자</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">㳞|–|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">㳞
@@ -1834,33 +191,7 @@
     <t xml:space="preserve">△</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">湳|–|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">湳
@@ -1868,98 +199,10 @@
 㳞</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">추정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">湳(氵南) 추정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㳞|㳞|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">㳞
@@ -1970,33 +213,7 @@
     <t xml:space="preserve">을</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潕</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">潕|–|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">潕
@@ -2007,92 +224,13 @@
     <t xml:space="preserve">사시</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潕</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">추정</t>
-    </r>
+    <t xml:space="preserve">潕(氵無) 추정</t>
   </si>
   <si>
     <t xml:space="preserve">潢</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">無|姑|–</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2106,42 +244,7 @@
     <t xml:space="preserve">상단 변 흐림</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㑖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㑖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">㑖|㑖|–</t>
   </si>
   <si>
     <t xml:space="preserve">㑖
@@ -2149,71 +252,10 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">亻仲 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">개 추정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">亻仲 2개 추정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南|南|–</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -2230,33 +272,7 @@
     <t xml:space="preserve">랑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">潢|無</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -2266,51 +282,7 @@
     <t xml:space="preserve">氵黃</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">無|南|仲</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2318,51 +290,7 @@
 仲</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
+    <t xml:space="preserve">姑|仲|姑</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -2373,33 +301,7 @@
     <t xml:space="preserve">의</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">南|南</t>
   </si>
   <si>
     <t xml:space="preserve">南
@@ -2418,33 +320,7 @@
     <t xml:space="preserve">나</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">姑|–|仲</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -2452,45 +328,11 @@
 仲</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">–|㳞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+㳞</t>
   </si>
   <si>
     <t xml:space="preserve">바구</t>
@@ -2499,33 +341,7 @@
     <t xml:space="preserve">氵仲</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">仲|–|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -2536,33 +352,7 @@
     <t xml:space="preserve">니들</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">仲|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -2572,33 +362,7 @@
     <t xml:space="preserve">러메</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">汰|–|仲</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -2609,83 +373,13 @@
     <t xml:space="preserve">고꽃</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵太</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">汰(氵太)</t>
   </si>
   <si>
     <t xml:space="preserve">팔</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">無|仲|–</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2699,33 +393,7 @@
     <t xml:space="preserve">왔소</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">㳞|–|仲</t>
   </si>
   <si>
     <t xml:space="preserve">㳞
@@ -2736,42 +404,7 @@
     <t xml:space="preserve">붉은</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">汰|㳞|–</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -2785,33 +418,7 @@
     <t xml:space="preserve">㳞</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">無|潢</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2821,33 +428,7 @@
     <t xml:space="preserve">보</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">㳞|潢</t>
   </si>
   <si>
     <t xml:space="preserve">㳞
@@ -2857,33 +438,7 @@
     <t xml:space="preserve">라</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
+    <t xml:space="preserve">無|姑</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2902,51 +457,7 @@
     <t xml:space="preserve">남</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">仲|仲|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -2966,24 +477,7 @@
     <t xml:space="preserve">봄</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">無|–</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -2993,51 +487,7 @@
     <t xml:space="preserve">흥</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">無|南|南</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -3051,51 +501,7 @@
     <t xml:space="preserve">불긋</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">潢|無|潢</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3106,98 +512,10 @@
     <t xml:space="preserve">아</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵黃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵黃</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">氵黃/無/氵黃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姑|仲|仲</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -3214,71 +532,10 @@
     <t xml:space="preserve">–</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">동그라미 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">동그라미 2개</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仲|㳞|–</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -3295,57 +552,14 @@
     <t xml:space="preserve">메고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">潢|–</t>
   </si>
   <si>
     <t xml:space="preserve">潢
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">無|無</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -3358,33 +572,7 @@
     <t xml:space="preserve">둘째 無 변 흐림</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">無|–|潢</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -3401,33 +589,7 @@
     <t xml:space="preserve">방</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">潢|潢</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3437,62 +599,10 @@
     <t xml:space="preserve">긋</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">둘째 흐림</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">南|? 둘째 흐림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">潢|–|仲</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3500,33 +610,7 @@
 仲</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">潢|㳞</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3536,103 +620,17 @@
     <t xml:space="preserve">웃는</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵黃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵仲</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">氵黃/氵仲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–|仲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+仲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">潢|汰</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -3642,62 +640,10 @@
     <t xml:space="preserve">활</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵黃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵太</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">太</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">氵黃/氵太</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太|汰</t>
   </si>
   <si>
     <t xml:space="preserve">太
@@ -3707,33 +653,7 @@
     <t xml:space="preserve">짝</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
+    <t xml:space="preserve">汰|汰</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -3743,65 +663,13 @@
     <t xml:space="preserve">피었</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">氵太 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
+    <t xml:space="preserve">氵太 2개</t>
   </si>
   <si>
     <t xml:space="preserve">네</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">汰|南</t>
   </si>
   <si>
     <t xml:space="preserve">汰
@@ -3826,42 +694,7 @@
     <t xml:space="preserve">꽃을사</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">姑|姑|–</t>
   </si>
   <si>
     <t xml:space="preserve">姑
@@ -3869,42 +702,7 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|–</t>
-    </r>
+    <t xml:space="preserve">仲|仲|–</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -3912,51 +710,7 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲</t>
-    </r>
+    <t xml:space="preserve">無|姑|仲</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -3997,24 +751,9 @@
 랑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+    <t xml:space="preserve">–
+㳞
 㳞</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">시
@@ -4031,23 +770,8 @@
 의</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
+    <t xml:space="preserve">–
+㳞</t>
   </si>
   <si>
     <t xml:space="preserve">사
@@ -4069,31 +793,9 @@
 로</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+    <t xml:space="preserve">湳
+㳞
+–</t>
   </si>
   <si>
     <t xml:space="preserve">파
@@ -4233,23 +935,8 @@
 –</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">–
+㴌</t>
   </si>
   <si>
     <t xml:space="preserve">㴌</t>
@@ -4258,24 +945,9 @@
     <t xml:space="preserve">홍</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
+    <t xml:space="preserve">–
+㳞
 㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">메
@@ -8146,7 +4818,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:M18"/>
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -8166,8 +4838,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="23" width="5.69"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
       <c r="B2" s="24" t="s">
         <v>208</v>
       </c>
@@ -8183,7 +4855,7 @@
       <c r="L2" s="24"/>
       <c r="M2" s="24"/>
     </row>
-    <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B3" s="25" t="s">
         <v>209</v>
       </c>
@@ -8221,7 +4893,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B4" s="25" t="s">
         <v>216</v>
       </c>
@@ -8259,7 +4931,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B5" s="25" t="s">
         <v>47</v>
       </c>
@@ -8295,7 +4967,7 @@
       </c>
       <c r="M5" s="29"/>
     </row>
-    <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B6" s="25" t="s">
         <v>152</v>
       </c>
@@ -8329,7 +5001,7 @@
       </c>
       <c r="M6" s="31"/>
     </row>
-    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B7" s="27" t="s">
         <v>55</v>
       </c>
@@ -8361,7 +5033,7 @@
       </c>
       <c r="M7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B8" s="25" t="s">
         <v>58</v>
       </c>
@@ -8393,7 +5065,7 @@
       </c>
       <c r="M8" s="29"/>
     </row>
-    <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B9" s="27" t="s">
         <v>209</v>
       </c>
@@ -8421,7 +5093,7 @@
       </c>
       <c r="M9" s="29"/>
     </row>
-    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B10" s="27" t="s">
         <v>64</v>
       </c>
@@ -8453,7 +5125,7 @@
       </c>
       <c r="M10" s="31"/>
     </row>
-    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B11" s="27" t="s">
         <v>203</v>
       </c>
@@ -8491,7 +5163,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B12" s="25" t="s">
         <v>205</v>
       </c>
@@ -8529,7 +5201,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B13" s="25" t="s">
         <v>73</v>
       </c>
@@ -8567,7 +5239,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B14" s="25" t="s">
         <v>256</v>
       </c>
@@ -8605,7 +5277,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B15" s="27" t="s">
         <v>145</v>
       </c>
@@ -8643,7 +5315,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B16" s="25" t="s">
         <v>81</v>
       </c>
@@ -8681,7 +5353,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B17" s="25" t="s">
         <v>83</v>
       </c>
@@ -8719,7 +5391,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B18" s="25" t="s">
         <v>278</v>
       </c>
@@ -8763,7 +5435,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리)-2.xlsx
@@ -4824,17 +4824,17 @@
   <sheetFormatPr defaultColWidth="8.0625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="23" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="23" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="23" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="23" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="23" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="22" width="11.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="22" width="13.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="23" width="5.69"/>
   </cols>
   <sheetData>
